--- a/admin/개인별 주간 진행사항-박진영.xlsx
+++ b/admin/개인별 주간 진행사항-박진영.xlsx
@@ -610,30 +610,43 @@
       </x:c>
       <x:c r="C8" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">캡스톤 회의자료 14p 작성 (아키텍처·역할·로드맵·비용 분석)
-팀원 역할 최종 배분(A/B/C/D1/D2)
-CI/CD + pre-commit + 테스트 22개 구축
-CLAUDE.md 603줄 팀 컨벤션 문서 작성</x:t>
+          <x:t xml:space="preserve">캡스톤 회의자료 14p 작성
+(아키텍처·역할·로드맵·비용 분석)</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">실제 개발 착수 — 환경 기동
-API 키 발급
-Kafka→cron+INSERT 전환
-XGBoost 학습 데이터 확보</x:t>
+          <x:t xml:space="preserve">실제 개발 착수 — 환경 기동</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4">
       <x:c r="B9" s="4"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
+      <x:c r="C9" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">팀원 역할 최종 배분(A/B/C/D1/D2)
+CI/CD + pre-commit + 테스트 22개 구축</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">API 키 발급
+Kafka→cron+INSERT 전환</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="10" spans="2:4">
       <x:c r="B10" s="4"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
+      <x:c r="C10" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CLAUDE.md 603줄 팀 컨벤션 문서 작성</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">XGBoost 학습 데이터 확보</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="11" spans="2:4">
       <x:c r="B11" s="4" t="s">
@@ -642,31 +655,43 @@
       <x:c r="C11" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Docker Compose 인프라 기동 + health check
-Kafka→cron+INSERT 마이그레이션
-KDCA 인플루엔자 공공데이터 확보
-+ XGBoost walk-forward 학습 (F1≥0.70)
-Autoencoder fit() + 체크포인트 생성
-ml/serve.py 추론 엔드포인트 연결
-E2E 시연 테스트 (수집→DB→API→대시보드)</x:t>
+Kafka→cron+INSERT 마이그레이션</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RAG 역학 문서 임베딩 (5~10편)
-경보 리포트 생성 E2E
-Autoencoder threshold 최적화</x:t>
+          <x:t xml:space="preserve">RAG 역학 문서 임베딩 (5~10편)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4">
       <x:c r="B12" s="4"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
+      <x:c r="C12" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">KDCA 인플루엔자 공공데이터 확보
+XGBoost walk-forward 학습 (F1≥0.70)
+Autoencoder fit() + 체크포인트 생성</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">경보 리포트 생성 E2E</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="13" spans="2:4">
       <x:c r="B13" s="4"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
+      <x:c r="C13" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ml/serve.py 추론 엔드포인트 연결
+E2E 시연 테스트 (수집→DB→API→대시보드)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Autoencoder threshold 최적화</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="14" spans="2:4">
       <x:c r="B14" s="4" t="s">
